--- a/notebooks/segmentation result.xlsx
+++ b/notebooks/segmentation result.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OutlesClassifier-ChatAssist\notebooks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C5CE39-8FD0-434C-8FCC-B3FF29D42309}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,100 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>Segment Name</t>
+  </si>
+  <si>
+    <t>Key Characteristics</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Unique Products</t>
+  </si>
+  <si>
+    <t>Avg Sales / Product</t>
+  </si>
+  <si>
+    <t>Total Pieces</t>
+  </si>
+  <si>
+    <t>Total KG/Litre</t>
+  </si>
+  <si>
+    <t>Outlet Class Mix</t>
+  </si>
+  <si>
+    <t>Mid-Value Balanced Outlets</t>
+  </si>
+  <si>
+    <t>Moderate sales, decent product variety, general-purpose outlets, not highly specialized</t>
+  </si>
+  <si>
+    <t>C (43.54%), D (27.34%), B (17.35%), A (11.77%)</t>
+  </si>
+  <si>
+    <t>Low-Value Efficient Outlets</t>
+  </si>
+  <si>
+    <t>Smaller outlets, fewer products, but high efficiency per product; focused selling</t>
+  </si>
+  <si>
+    <t>D (44.48%), C (38.10%), B (10.52%), A (6.88%)</t>
+  </si>
+  <si>
+    <t>Ultra-Premium Niche Accounts</t>
+  </si>
+  <si>
+    <t>Extremely high sales, massive transactions, niche or bulk specialists, very high impact</t>
+  </si>
+  <si>
+    <t>A (80.00%), C (10.00%), D (10.00%)</t>
+  </si>
+  <si>
+    <t>Elite High-Value Performers</t>
+  </si>
+  <si>
+    <t>High sales + strong product mix, consistent top performers, large-scale outlets</t>
+  </si>
+  <si>
+    <t>A (83.53%), D (9.41%), 
+B (3.53%), 
+C (3.53%)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="174" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -46,13 +142,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +455,165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="20.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="7" customWidth="1"/>
+    <col min="5" max="7" width="11.42578125" style="7"/>
+    <col min="8" max="8" width="11.42578125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5">
+        <v>63350.95</v>
+      </c>
+      <c r="E2" s="2">
+        <v>22.38</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1586.17</v>
+      </c>
+      <c r="G2" s="2">
+        <v>733.26</v>
+      </c>
+      <c r="H2" s="6">
+        <v>396.93</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5">
+        <v>25616.11</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.15</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2025.99</v>
+      </c>
+      <c r="G3" s="2">
+        <v>257.08</v>
+      </c>
+      <c r="H3" s="6">
+        <v>155.41999999999999</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5">
+        <v>14016689.140000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="F4" s="4">
+        <v>837754</v>
+      </c>
+      <c r="G4" s="4">
+        <v>98390</v>
+      </c>
+      <c r="H4" s="6">
+        <v>108569.89</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3152058.4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>14.68</v>
+      </c>
+      <c r="F5" s="4">
+        <v>137210.43</v>
+      </c>
+      <c r="G5" s="4">
+        <v>23819.21</v>
+      </c>
+      <c r="H5" s="6">
+        <v>17630.95</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/notebooks/segmentation result.xlsx
+++ b/notebooks/segmentation result.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OutlesClassifier-ChatAssist\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C5CE39-8FD0-434C-8FCC-B3FF29D42309}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A50D2F-63F8-45A3-BD90-77C2684153E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
   <si>
     <t>Cluster</t>
   </si>
@@ -60,36 +67,1048 @@
     <t>Moderate sales, decent product variety, general-purpose outlets, not highly specialized</t>
   </si>
   <si>
-    <t>C (43.54%), D (27.34%), B (17.35%), A (11.77%)</t>
-  </si>
-  <si>
     <t>Low-Value Efficient Outlets</t>
   </si>
   <si>
     <t>Smaller outlets, fewer products, but high efficiency per product; focused selling</t>
   </si>
   <si>
-    <t>D (44.48%), C (38.10%), B (10.52%), A (6.88%)</t>
-  </si>
-  <si>
     <t>Ultra-Premium Niche Accounts</t>
   </si>
   <si>
     <t>Extremely high sales, massive transactions, niche or bulk specialists, very high impact</t>
   </si>
   <si>
-    <t>A (80.00%), C (10.00%), D (10.00%)</t>
-  </si>
-  <si>
     <t>Elite High-Value Performers</t>
   </si>
   <si>
     <t>High sales + strong product mix, consistent top performers, large-scale outlets</t>
   </si>
   <si>
-    <t>A (83.53%), D (9.41%), 
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>It should be absolute</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>diamond</t>
+  </si>
+  <si>
+    <t>platinum</t>
+  </si>
+  <si>
+    <t>Avg Sales/ per outlet per month</t>
+  </si>
+  <si>
+    <t>Unique SKUs (list</t>
+  </si>
+  <si>
+    <t>C (43.54%), 
+D (27.34%), 
+B (17.35%), 
+A (11.77%)</t>
+  </si>
+  <si>
+    <t>D (44.48%), 
+C (38.10%), 
+B (10.52%), 
+A (6.88%)</t>
+  </si>
+  <si>
+    <t>Buying Frequency</t>
+  </si>
+  <si>
+    <t>A (80.00%), 
+C (10.00%), 
+D (10.00%)</t>
+  </si>
+  <si>
+    <t>A (83.53%), 
+D (9.41%), 
 B (3.53%), 
 C (3.53%)</t>
+  </si>
+  <si>
+    <t>Sales(Low-Medium-High),
+Product Variety(SKU trend), 
+Ocassion Buyer (buying frequency)</t>
+  </si>
+  <si>
+    <t>Cluster Total Sales</t>
+  </si>
+  <si>
+    <t>SKU wise Break-up</t>
+  </si>
+  <si>
+    <t>Small Kirana Store</t>
+  </si>
+  <si>
+    <t>Basic Kirana Store</t>
+  </si>
+  <si>
+    <t>Modern Kirana Store</t>
+  </si>
+  <si>
+    <t>Supermarket</t>
+  </si>
+  <si>
+    <t>ShoperMart</t>
+  </si>
+  <si>
+    <t>ASO</t>
+  </si>
+  <si>
+    <t>Avg Sales</t>
+  </si>
+  <si>
+    <t>SKU count</t>
+  </si>
+  <si>
+    <t>Store name</t>
+  </si>
+  <si>
+    <t>Buying Frequecny</t>
+  </si>
+  <si>
+    <t>Wallet Share</t>
+  </si>
+  <si>
+    <t>60 stores</t>
+  </si>
+  <si>
+    <t>High-Value, High-Volume Performers, Elite Outlets</t>
+  </si>
+  <si>
+    <t>Premium, Ultra-High Volume/Value, Niche Specialists</t>
+  </si>
+  <si>
+    <t>Mid-Value, Balanced Outlets</t>
+  </si>
+  <si>
+    <t>Lower-Value, High Average Sales Efficiency, Emerging/Smaller Outlets</t>
+  </si>
+  <si>
+    <t>Key Characteristics &amp; Behavioral Definition</t>
+  </si>
+  <si>
+    <t>Statistical/Mathematical Behavior (Mean Values)</t>
+  </si>
+  <si>
+    <t>Cluster 0</t>
+  </si>
+  <si>
+    <r>
+      <t>Mid-Value, Balanced Outlets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> These are general-purpose outlets with moderate overall sales and a reasonable variety of products. They show a balanced performance across most metrics and are less specialized than other clusters. Diverse in Outlet Class, with 'C' and 'D' being prominent.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Sales:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>63797.82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unique Products:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>17.82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avg Sales Per Product:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>3101.70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Pieces Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>647.55</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total KG/Litre Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>385.24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outlet Class Distribution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> C (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>42.05%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), D (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>28.71%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), B (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>16.67%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), A (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>12.57%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cluster 1</t>
+  </si>
+  <si>
+    <r>
+      <t>Lower-Value, High Average Sales Efficiency, Emerging/Smaller Outlets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> These outlets have lower total sales and fewer unique products, suggesting a smaller scale of operation. However, their </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Avg_Sales_Per_Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> is notably higher than Cluster 0, indicating they might focus on selling fewer, higher-value items or achieve good efficiency per product sold. Predominantly 'D' class, indicating smaller or less active outlets.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Sales:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>21042.08</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unique Products:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>6.72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avg Sales Per Product:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>2653.45</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Pieces Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>199.81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total KG/Litre Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>126.03</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outlet Class Distribution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> A (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>8.25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), D (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>40.36%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), C (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>39.54%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), B (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>11.83%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cluster 2</t>
+  </si>
+  <si>
+    <r>
+      <t>Premium, Ultra-High Volume/Value, Niche Specialists:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> This is a distinct, small cluster representing an extreme, high-impact segment. They exhibit astronomical total sales and average sales per product, signifying either very large volume transactions or extremely high-value products. While not having the most unique products, their financial impact is immense. Overwhelmingly dominated by 'A' class outlets, suggesting flagship stores or key accounts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Sales:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>5365478.61</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unique Products:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>9.32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avg Sales Per Product:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>430487.65</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Pieces Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>39255.37</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total KG/Litre Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>30478.98</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outlet Class Distribution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> A (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>89.47%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), B (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>10.53%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), C (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), D (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cluster 3</t>
+  </si>
+  <si>
+    <r>
+      <t>High-Value, High-Volume Performers, Elite Outlets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> These outlets are strong performers with high total sales, a significant number of unique products, and very high total pieces and KG/Litre sold. Their </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Avg_Sales_Per_Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> is also very high, reflecting a combination of high volume and value. Heavily skewed towards 'A' class outlets, indicating top-tier retail partners or major accounts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Sales:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>14529832.49</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unique Products:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>13.00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avg Sales Per Product:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>908114.53</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Pieces Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>71901.00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total KG/Litre Sold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>358696.71</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outlet Class Distribution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> C (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>100.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), A (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), B (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), D (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE3E3E3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Segment</t>
   </si>
 </sst>
 </file>
@@ -98,10 +1117,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;₹&quot;\ #,##0"/>
-    <numFmt numFmtId="174" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,16 +1143,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFE3E3E3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE3E3E3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFE3E3E3"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF282A2C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -141,39 +1199,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -456,164 +1575,542 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T14"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="9"/>
-    <col min="2" max="2" width="20.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="7" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="7"/>
-    <col min="8" max="8" width="11.42578125" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="7"/>
+    <col min="1" max="1" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="20.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="2" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="2"/>
+    <col min="11" max="11" width="36.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" style="2"/>
+    <col min="18" max="18" width="14.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="24" style="2" customWidth="1"/>
+    <col min="20" max="20" width="18.44140625" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="J1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="5"/>
+      <c r="L1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="20">
         <v>63350.95</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="19">
         <v>22.38</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="21">
         <v>1586.17</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="19">
         <v>733.26</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="22">
         <v>396.93</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="S2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="20">
+        <v>25616.11</v>
+      </c>
+      <c r="E3" s="19">
+        <v>8.15</v>
+      </c>
+      <c r="F3" s="21">
+        <v>2025.99</v>
+      </c>
+      <c r="G3" s="19">
+        <v>257.08</v>
+      </c>
+      <c r="H3" s="22">
+        <v>155.41999999999999</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="S3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5">
-        <v>25616.11</v>
-      </c>
-      <c r="E3" s="2">
-        <v>8.15</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2025.99</v>
-      </c>
-      <c r="G3" s="2">
-        <v>257.08</v>
-      </c>
-      <c r="H3" s="6">
-        <v>155.41999999999999</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="C4" s="19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="20">
+        <v>14016689.140000001</v>
+      </c>
+      <c r="E4" s="19">
+        <v>11.3</v>
+      </c>
+      <c r="F4" s="21">
+        <v>837754</v>
+      </c>
+      <c r="G4" s="21">
+        <v>98390</v>
+      </c>
+      <c r="H4" s="22">
+        <v>108569.89</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="S4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5">
-        <v>14016689.140000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>11.3</v>
-      </c>
-      <c r="F4" s="4">
-        <v>837754</v>
-      </c>
-      <c r="G4" s="4">
-        <v>98390</v>
-      </c>
-      <c r="H4" s="6">
-        <v>108569.89</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="D5" s="20">
+        <v>3152058.4</v>
+      </c>
+      <c r="E5" s="19">
+        <v>14.68</v>
+      </c>
+      <c r="F5" s="21">
+        <v>137210.43</v>
+      </c>
+      <c r="G5" s="21">
+        <v>23819.21</v>
+      </c>
+      <c r="H5" s="22">
+        <v>17630.95</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="S5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D9" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5">
-        <v>3152058.4</v>
-      </c>
-      <c r="E5" s="2">
-        <v>14.68</v>
-      </c>
-      <c r="F5" s="4">
-        <v>137210.43</v>
-      </c>
-      <c r="G5" s="4">
-        <v>23819.21</v>
-      </c>
-      <c r="H5" s="6">
-        <v>17630.95</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="K12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="R12" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="L14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L12:O12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F29439-0561-41E6-9A3A-8A8000F5764F}">
+  <dimension ref="A2:C32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.44140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="94.33203125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="91" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="14">
+        <v>908114.53062500001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="14">
+        <v>358958.07612699998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="14">
+        <v>2637.3785109999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="14">
+        <v>2509.3980499999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B21:B26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>